--- a/Tests/Fixtures/openpyxl_generated.xlsx
+++ b/Tests/Fixtures/openpyxl_generated.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="TestSheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SecondSheet" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -29,7 +32,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Comic Sans MS"/>
       <b val="1"/>
+      <i val="1"/>
       <color rgb="00FF0000"/>
     </font>
   </fonts>
@@ -47,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +455,11 @@
           <t>Styled</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Merged Area</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -450,6 +469,41 @@
     <row r="3">
       <c r="A3" t="n">
         <v>3.1415</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45440.60416666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>SUM(A2:A3)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data in second sheet</t>
+        </is>
       </c>
     </row>
   </sheetData>
